--- a/output/pdf_financials_xlsx/EDCU.xlsx
+++ b/output/pdf_financials_xlsx/EDCU.xlsx
@@ -5390,49 +5390,49 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.165789</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.58657</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.816792</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.729683</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.596044</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.742138</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.529416</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.523913</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.670829</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.658235</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.663416</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.693874</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.732046</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.70561</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.249345</v>
       </c>
     </row>
     <row r="93">
@@ -6778,31 +6778,31 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.782385</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-3.321954</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-1.966772</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.135074</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.243989</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>3.231634</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>1.152746</v>
+        <v>0.767087</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>1.444511</v>
+        <v>1.333175</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.773325</v>
+        <v>0.723573</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>0</v>
@@ -9318,7 +9318,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10117,7 +10121,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11272,7 +11280,11 @@
           <t>Reserves 8 666,267</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -12568,7 +12580,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -13773,7 +13789,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -14695,7 +14715,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -15419,7 +15443,11 @@
           <t>Reserves (note 8)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -16131,7 +16159,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -17450,7 +17482,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -19555,7 +19591,11 @@
           <t>Reserves (note 8)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E130" s="5" t="n">
         <v>0.165789</v>
       </c>
@@ -22445,7 +22485,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/EDCU.xlsx
+++ b/output/pdf_financials_xlsx/EDCU.xlsx
@@ -993,28 +993,28 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.017388</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.02045</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004933</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001395</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.037952</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.005369</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000266</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000973</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.006861</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.008208999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.07739699999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1899,28 +1899,28 @@
         <v>-0.9172</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.067468</v>
+        <v>-1.084856</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.092177</v>
+        <v>-2.112627</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.102677</v>
+        <v>-1.10761</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.113315</v>
+        <v>-1.11471</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.998665</v>
+        <v>-3.036617</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.078946</v>
+        <v>-1.084315</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.16556</v>
+        <v>-1.165826</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.685427</v>
+        <v>-0.6864</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.053951</v>
@@ -1929,13 +1929,13 @@
         <v>-0.056598</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.048374</v>
+        <v>-0.055235</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.010449</v>
+        <v>0.00224</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>5.299675</v>
+        <v>5.222278</v>
       </c>
     </row>
     <row r="28">
@@ -2007,28 +2007,28 @@
         <v>-0.910493</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.063243</v>
+        <v>-1.080631</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.090554</v>
+        <v>-2.111004</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.10117</v>
+        <v>-1.106103</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.106354</v>
+        <v>-1.107749</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.997882</v>
+        <v>-3.035834</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.078619</v>
+        <v>-1.083988</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.152032</v>
+        <v>-1.152298</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.664737</v>
+        <v>-0.66571</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.053951</v>
@@ -2037,13 +2037,13 @@
         <v>-0.056598</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.048374</v>
+        <v>-0.055235</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.010449</v>
+        <v>0.00224</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.299675</v>
+        <v>5.222278</v>
       </c>
     </row>
     <row r="30">
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.310496</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>1.172112</v>
@@ -2299,16 +2299,16 @@
         <v>0.166718</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.172557</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.265682</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.197584</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.348813</v>
@@ -2320,7 +2320,7 @@
         <v>0.298252</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>10.346358</v>
       </c>
     </row>
     <row r="35">
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.310496</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>1.172112</v>
@@ -2403,16 +2403,16 @@
         <v>0.166718</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.172557</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.265682</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.197584</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.367</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.348813</v>
@@ -2424,7 +2424,7 @@
         <v>0.298252</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>10.346358</v>
       </c>
     </row>
     <row r="37">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.313768</v>
+        <v>0.003272</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.145892</v>
@@ -3027,16 +3027,16 @@
         <v>0.007397</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.18002</v>
+        <v>0.007463</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.273279</v>
+        <v>0.007597</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.201825</v>
+        <v>0.004241</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.221114</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>10.877344</v>
+        <v>0.530986</v>
       </c>
     </row>
     <row r="49">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -12675,7 +12675,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -33111,7 +33111,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -40353,7 +40353,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -40539,7 +40539,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -43168,7 +43168,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -43354,7 +43354,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -45158,7 +45158,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -45344,7 +45344,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -47027,7 +47027,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -47844,7 +47844,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
